--- a/budget/NNF_NERD_budget_template_NAT_08012026_2025_project_supplement_MBG.xlsx
+++ b/budget/NNF_NERD_budget_template_NAT_08012026_2025_project_supplement_MBG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kmt/application-nerd-2026/budget/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEA7A5EE-86D2-4D48-A081-0084895FF2BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBBDC31-E740-5746-829A-E83F7E58669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{D494D1E6-F797-4A73-AFC2-FF09A684A778}"/>
+    <workbookView xWindow="1140" yWindow="660" windowWidth="33440" windowHeight="21680" activeTab="4" xr2:uid="{D494D1E6-F797-4A73-AFC2-FF09A684A778}"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="14" r:id="rId1"/>
@@ -27469,7 +27469,7 @@
       <c r="AA97" s="82"/>
       <c r="AB97" s="72"/>
       <c r="AC97" s="52">
-        <v>90000</v>
+        <v>100000</v>
       </c>
       <c r="AD97" s="72"/>
       <c r="AE97" s="72"/>
@@ -27487,7 +27487,7 @@
       <c r="AQ97" s="72"/>
       <c r="AR97" s="81">
         <f t="shared" si="133"/>
-        <v>590000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="98" spans="2:44" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -28803,7 +28803,7 @@
       <c r="AB121" s="106"/>
       <c r="AC121" s="74">
         <f>SUM(AC95:AC120)</f>
-        <v>235000</v>
+        <v>245000</v>
       </c>
       <c r="AD121" s="90"/>
       <c r="AE121" s="90"/>
@@ -28833,7 +28833,7 @@
       <c r="AQ121" s="80"/>
       <c r="AR121" s="75">
         <f>SUM(N121:AO121)</f>
-        <v>2955000</v>
+        <v>2965000</v>
       </c>
     </row>
     <row r="122" spans="2:44" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -30401,7 +30401,7 @@
       <c r="AB150" s="450"/>
       <c r="AC150" s="451">
         <f>AC121</f>
-        <v>235000</v>
+        <v>245000</v>
       </c>
       <c r="AD150" s="449"/>
       <c r="AE150" s="450"/>
@@ -30431,7 +30431,7 @@
       <c r="AQ150" s="450"/>
       <c r="AR150" s="453">
         <f>AR121</f>
-        <v>2955000</v>
+        <v>2965000</v>
       </c>
     </row>
     <row r="151" spans="2:70" ht="16.5" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -30588,7 +30588,7 @@
       <c r="AB153" s="408"/>
       <c r="AC153" s="409">
         <f>AC92+AC150</f>
-        <v>1386161.9380376781</v>
+        <v>1396161.9380376781</v>
       </c>
       <c r="AD153" s="407"/>
       <c r="AE153" s="408"/>
@@ -30618,7 +30618,7 @@
       <c r="AQ153" s="411"/>
       <c r="AR153" s="412">
         <f>SUM(N153:AO153)</f>
-        <v>12122339.392005179</v>
+        <v>12132339.392005179</v>
       </c>
       <c r="AS153"/>
       <c r="AT153"/>
@@ -30862,7 +30862,7 @@
       <c r="AA155" s="407"/>
       <c r="AB155" s="417">
         <f>IFERROR((AC155/IF($F$180="Total",SUM(AC153,AC155),AC153)), "")</f>
-        <v>0.21292760870010199</v>
+        <v>0.21172541705332343</v>
       </c>
       <c r="AC155" s="418" cm="1">
         <f t="array" ref="AC155">IF(
@@ -30922,7 +30922,7 @@
       <c r="AP155" s="419"/>
       <c r="AQ155" s="417">
         <f>IFERROR((AR155/IF($F$180="Total",SUM(AR153,AR155),AR153)), "")</f>
-        <v>0.22403814897217922</v>
+        <v>0.22389483187589945</v>
       </c>
       <c r="AR155" s="412">
         <f>SUM(N155,Q155,T155,W155,Z155,AC155,AF155,AI155,AL155,AO155)</f>
@@ -31142,7 +31142,7 @@
       <c r="AB157" s="358"/>
       <c r="AC157" s="359">
         <f>SUM(AC153:AC156)</f>
-        <v>1761161.9380376781</v>
+        <v>1771161.9380376781</v>
       </c>
       <c r="AD157" s="357"/>
       <c r="AE157" s="358"/>
@@ -31172,7 +31172,7 @@
       <c r="AQ157" s="358"/>
       <c r="AR157" s="360">
         <f>SUM(L157:AO157)</f>
-        <v>15622339.392005179</v>
+        <v>15632339.392005179</v>
       </c>
       <c r="AS157"/>
       <c r="AT157"/>
@@ -31930,7 +31930,7 @@
       <c r="AB166" s="502"/>
       <c r="AC166" s="501">
         <f>SUM(AC157,AC164)</f>
-        <v>1761161.9380376781</v>
+        <v>1771161.9380376781</v>
       </c>
       <c r="AD166" s="502"/>
       <c r="AE166" s="502"/>
@@ -31960,7 +31960,7 @@
       <c r="AQ166" s="502"/>
       <c r="AR166" s="504">
         <f>SUM(L166:AO166)</f>
-        <v>15622339.392005179</v>
+        <v>15632339.392005179</v>
       </c>
     </row>
     <row r="168" spans="2:70" x14ac:dyDescent="0.2">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="AQ168" s="78">
         <f>((AP154+AR155+(2*300000))/(AR157-AR95))*100</f>
-        <v>26.447621202993659</v>
+        <v>26.430571794432741</v>
       </c>
     </row>
     <row r="169" spans="2:70" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -40707,7 +40707,7 @@
       </c>
       <c r="I78" s="149">
         <f>AU!AC97</f>
-        <v>90000</v>
+        <v>100000</v>
       </c>
       <c r="J78" s="149">
         <f>AU!AF97</f>
@@ -40727,7 +40727,7 @@
       </c>
       <c r="N78" s="155">
         <f t="shared" ref="N78:N93" si="14">SUM(D78:M78)</f>
-        <v>590000</v>
+        <v>600000</v>
       </c>
       <c r="Q78" s="267" t="str">
         <f>AU!C125</f>
@@ -43199,7 +43199,7 @@
       </c>
       <c r="I102" s="170">
         <f t="shared" si="20"/>
-        <v>235000</v>
+        <v>245000</v>
       </c>
       <c r="J102" s="170">
         <f t="shared" si="20"/>
@@ -43219,7 +43219,7 @@
       </c>
       <c r="N102" s="160">
         <f t="shared" si="20"/>
-        <v>2955000</v>
+        <v>2965000</v>
       </c>
       <c r="Q102" s="272" t="s">
         <v>120</v>
@@ -43349,7 +43349,7 @@
       </c>
       <c r="I105" s="481">
         <f>AU!AC153</f>
-        <v>1386161.9380376781</v>
+        <v>1396161.9380376781</v>
       </c>
       <c r="J105" s="481">
         <f>AU!AF153</f>
@@ -43369,7 +43369,7 @@
       </c>
       <c r="N105" s="482">
         <f>SUM(D105:M105)</f>
-        <v>12122339.392005179</v>
+        <v>12132339.392005179</v>
       </c>
       <c r="Q105" s="253" t="str">
         <f>"Total "&amp;AU!B159</f>
@@ -43657,7 +43657,7 @@
       </c>
       <c r="I108" s="491">
         <f t="shared" si="23"/>
-        <v>1761161.9380376781</v>
+        <v>1771161.9380376781</v>
       </c>
       <c r="J108" s="491">
         <f t="shared" si="23"/>
@@ -43677,7 +43677,7 @@
       </c>
       <c r="N108" s="492">
         <f>SUM(N105:N107)</f>
-        <v>15622339.392005179</v>
+        <v>15632339.392005179</v>
       </c>
       <c r="Q108" s="283" t="s">
         <v>120</v>
@@ -43854,7 +43854,7 @@
       </c>
       <c r="I111" s="513">
         <f t="shared" si="25"/>
-        <v>1761161.9380376781</v>
+        <v>1771161.9380376781</v>
       </c>
       <c r="J111" s="513">
         <f t="shared" si="25"/>
@@ -43874,7 +43874,7 @@
       </c>
       <c r="N111" s="514">
         <f>SUM(D111:M111)</f>
-        <v>15622339.392005179</v>
+        <v>15632339.392005179</v>
       </c>
       <c r="Q111" s="776" t="str">
         <f ca="1">ROUND(AU!$AQ$154*100,0)&amp;"% (of "&amp;IF(AU!F177="Total","direct costs+proj.suppl.","direct costs")&amp;IF(AU!F174="Yes"," excl. equipment","")&amp;")"</f>
@@ -47468,7 +47468,7 @@
       <c r="M41" s="647"/>
       <c r="N41" s="139">
         <f>AU!AC97</f>
-        <v>90000</v>
+        <v>100000</v>
       </c>
       <c r="O41" s="647"/>
       <c r="P41" s="139">
@@ -49089,7 +49089,7 @@
       <c r="B69" s="632"/>
       <c r="C69" s="632">
         <f>SUM(D69:W69)</f>
-        <v>15622339.392005179</v>
+        <v>15632339.392005179</v>
       </c>
       <c r="D69" s="638">
         <f>SUM(D5:D68)</f>
@@ -49118,7 +49118,7 @@
       <c r="M69" s="631"/>
       <c r="N69" s="630">
         <f>SUM(N5:N68)</f>
-        <v>1761161.9380376781</v>
+        <v>1771161.9380376781</v>
       </c>
       <c r="O69" s="637"/>
       <c r="P69" s="638">
